--- a/output_assignment1a.xlsx
+++ b/output_assignment1a.xlsx
@@ -427,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t># Setups</t>
+          <t>Num Setups</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
